--- a/src/nodes/HPC/compressor_stage_8_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_8_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00066802008821083541</v>
       </c>
       <c r="B2">
-        <v>0.000458260848226059</v>
+        <v>0.00050769433475366071</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0013360401764216708</v>
       </c>
       <c r="B3">
-        <v>0.00075105988682271367</v>
+        <v>0.00081919793582021876</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0020040602646325062</v>
       </c>
       <c r="B4">
-        <v>0.0010108344472685397</v>
+        <v>0.001093401730171399</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0026720803528433416</v>
       </c>
       <c r="B5">
-        <v>0.0012450892596466894</v>
+        <v>0.0013392800920844169</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0033401004410541766</v>
       </c>
       <c r="B6">
-        <v>0.0014569630133572516</v>
+        <v>0.0015605704450427295</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0040081205292650125</v>
       </c>
       <c r="B7">
-        <v>0.0016482940040039248</v>
+        <v>0.0017594525466822079</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0046761406174758479</v>
       </c>
       <c r="B8">
-        <v>0.0018202089306800018</v>
+        <v>0.0019372535837247232</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0053441607056866833</v>
       </c>
       <c r="B9">
-        <v>0.0019743871543231131</v>
+        <v>0.0020959668103774851</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0060121807938975178</v>
       </c>
       <c r="B10">
-        <v>0.0021126267367407589</v>
+        <v>0.0022377292691992613</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0066802008821083532</v>
       </c>
       <c r="B11">
-        <v>0.0022366478813755876</v>
+        <v>0.002364587088669727</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0073482209703191895</v>
       </c>
       <c r="B12">
-        <v>0.0023474039288308188</v>
+        <v>0.002477667370786917</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0080162410585300249</v>
       </c>
       <c r="B13">
-        <v>0.0024428586267168043</v>
+        <v>0.002574512025701396</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.00868426114674086</v>
       </c>
       <c r="B14">
-        <v>0.0025218168601521766</v>
+        <v>0.0026536734957044732</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0093522812349516957</v>
       </c>
       <c r="B15">
-        <v>0.0025894376572815664</v>
+        <v>0.0027213315434979134</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.01002030132316253</v>
       </c>
       <c r="B16">
-        <v>0.002650452541736399</v>
+        <v>0.0027831539056408523</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.010688321411373367</v>
       </c>
       <c r="B17">
-        <v>0.0027015288760692856</v>
+        <v>0.0028351328937114527</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.011356341499584201</v>
       </c>
       <c r="B18">
-        <v>0.0027383451053543738</v>
+        <v>0.00287207534535656</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.012024361587795036</v>
       </c>
       <c r="B19">
-        <v>0.0027606881658307695</v>
+        <v>0.0028937216274787119</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.012692381676005872</v>
       </c>
       <c r="B20">
-        <v>0.0027693721165288187</v>
+        <v>0.0029010454892943707</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.013360401764216707</v>
       </c>
       <c r="B21">
-        <v>0.0027652110164788687</v>
+        <v>0.0028950206800199977</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.014028421852427543</v>
       </c>
       <c r="B22">
-        <v>0.00274887174572406</v>
+        <v>0.0028764453539837243</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.014696441940638379</v>
       </c>
       <c r="B23">
-        <v>0.0027204324683587225</v>
+        <v>0.0028454152859603583</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.015364462028849214</v>
       </c>
       <c r="B24">
-        <v>0.0026798241694899797</v>
+        <v>0.0028018506558363768</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.01603248211706005</v>
       </c>
       <c r="B25">
-        <v>0.0026269778342249564</v>
+        <v>0.0027456716434982572</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.016700502205270883</v>
       </c>
       <c r="B26">
-        <v>0.0025617960695331152</v>
+        <v>0.0026767653829035442</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.017368522293481719</v>
       </c>
       <c r="B27">
-        <v>0.0024840679698332683</v>
+        <v>0.0025948868242940491</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.018036542381692555</v>
       </c>
       <c r="B28">
-        <v>0.0023935542514065679</v>
+        <v>0.00249975787198265</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.018704562469903391</v>
       </c>
       <c r="B29">
-        <v>0.0022900156305341647</v>
+        <v>0.002391100430282228</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.019372582558114228</v>
       </c>
       <c r="B30">
-        <v>0.0021733133528115977</v>
+        <v>0.0022687581341078412</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.020040602646325061</v>
       </c>
       <c r="B31">
-        <v>0.0020437107810919643</v>
+        <v>0.0021330615407832748</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.020708622734535897</v>
       </c>
       <c r="B32">
-        <v>0.0019015718075427463</v>
+        <v>0.0019844629382344942</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.021376642822746733</v>
       </c>
       <c r="B33">
-        <v>0.001747260324331429</v>
+        <v>0.0018234146143874643</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.022044662910957566</v>
       </c>
       <c r="B34">
-        <v>0.0015809626310883556</v>
+        <v>0.0016501570536521766</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.022712682999168402</v>
       </c>
       <c r="B35">
-        <v>0.0014021546572953088</v>
+        <v>0.0014640835263747267</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.023380703087379235</v>
       </c>
       <c r="B36">
-        <v>0.0012101347398969307</v>
+        <v>0.0012643754993852362</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.024048723175590071</v>
       </c>
       <c r="B37">
-        <v>0.001004201215837862</v>
+        <v>0.0010502144395138245</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.024716743263800908</v>
       </c>
       <c r="B38">
-        <v>0.00078322589406450214</v>
+        <v>0.0008202713572185602</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.025384763352011744</v>
       </c>
       <c r="B39">
-        <v>0.00054437447153028013</v>
+        <v>0.0005711754374692989</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.02605278344022258</v>
       </c>
       <c r="B40">
-        <v>0.00028438611719038166</v>
+        <v>0.00029904540886384231</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.02605278344022258</v>
       </c>
       <c r="B43">
-        <v>0.00013779320045577542</v>
+        <v>0.00012313390878231482</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.025384763352011744</v>
       </c>
       <c r="B44">
-        <v>0.00027636481214009354</v>
+        <v>0.00024956384620107493</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.024716743263800908</v>
       </c>
       <c r="B45">
-        <v>0.00041277126252392288</v>
+        <v>0.000375725799369865</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.024048723175590071</v>
       </c>
       <c r="B46">
-        <v>0.00054406897907823871</v>
+        <v>0.00049805575540227628</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.023380703087379235</v>
       </c>
       <c r="B47">
-        <v>0.00066772714501387863</v>
+        <v>0.00061348638552557338</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.022712682999168402</v>
       </c>
       <c r="B48">
-        <v>0.00078286596650113053</v>
+        <v>0.00072093709742171257</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.022044662910957566</v>
       </c>
       <c r="B49">
-        <v>0.00088901840545014643</v>
+        <v>0.0008198239828863253</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.021376642822746733</v>
       </c>
       <c r="B50">
-        <v>0.00098571742377107671</v>
+        <v>0.00090956313371504127</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.020708622734535897</v>
       </c>
       <c r="B51">
-        <v>0.0010726605006252687</v>
+        <v>0.00098976936993352082</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.020040602646325061</v>
       </c>
       <c r="B52">
-        <v>0.0011502031841788551</v>
+        <v>0.0010608524244875442</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.019372582558114228</v>
       </c>
       <c r="B53">
-        <v>0.0012188655398491651</v>
+        <v>0.0011234207585529221</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.018704562469903391</v>
       </c>
       <c r="B54">
-        <v>0.0012791676330535285</v>
+        <v>0.001178082833305465</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.018036542381692555</v>
       </c>
       <c r="B55">
-        <v>0.0013315180456457405</v>
+        <v>0.0012253144250696578</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.017368522293481719</v>
       </c>
       <c r="B56">
-        <v>0.0013758794252254623</v>
+        <v>0.0012650605707646815</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.016700502205270883</v>
       </c>
       <c r="B57">
-        <v>0.0014121029358288208</v>
+        <v>0.0012971336224583917</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.01603248211706005</v>
       </c>
       <c r="B58">
-        <v>0.0014400397414919442</v>
+        <v>0.0013213459322186432</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.015364462028849214</v>
       </c>
       <c r="B59">
-        <v>0.0014595593060260058</v>
+        <v>0.0013375328196796085</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.014696441940638379</v>
       </c>
       <c r="B60">
-        <v>0.0014706042923423623</v>
+        <v>0.0013456214747407265</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.014028421852427543</v>
       </c>
       <c r="B61">
-        <v>0.0014731356631274171</v>
+        <v>0.0013455620548677529</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.013360401764216707</v>
       </c>
       <c r="B62">
-        <v>0.0014671143810675732</v>
+        <v>0.001337304717526444</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.012692381676005872</v>
       </c>
       <c r="B63">
-        <v>0.0014526383888733014</v>
+        <v>0.00132096501610775</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.012024361587795036</v>
       </c>
       <c r="B64">
-        <v>0.0014303535493513445</v>
+        <v>0.0012973200877034021</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.011356341499584201</v>
       </c>
       <c r="B65">
-        <v>0.0014010427053325124</v>
+        <v>0.0012673124653303262</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.010688321411373367</v>
       </c>
       <c r="B66">
-        <v>0.0013654886996476152</v>
+        <v>0.0012318846820054481</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.01002030132316253</v>
       </c>
       <c r="B67">
-        <v>0.0013234389026918665</v>
+        <v>0.0011907375387874134</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0093522812349516957</v>
       </c>
       <c r="B68">
-        <v>0.0012704987951180928</v>
+        <v>0.0011386049089017456</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.00868426114674086</v>
       </c>
       <c r="B69">
-        <v>0.0012032505046292109</v>
+        <v>0.0010713938690769145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0080162410585300249</v>
       </c>
       <c r="B70">
-        <v>0.0011263246368708897</v>
+        <v>0.00099467123788629847</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0073482209703191895</v>
       </c>
       <c r="B71">
-        <v>0.0010447695092698401</v>
+        <v>0.00091450606731374251</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0066802008821083532</v>
       </c>
       <c r="B72">
-        <v>0.00095725580843419563</v>
+        <v>0.00082931660114005665</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0060121807938975178</v>
       </c>
       <c r="B73">
-        <v>0.00086160141215573438</v>
+        <v>0.000736498879697232</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0053441607056866833</v>
       </c>
       <c r="B74">
-        <v>0.00075859059377939258</v>
+        <v>0.0006370109377250206</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0046761406174758479</v>
       </c>
       <c r="B75">
-        <v>0.00064976240023278682</v>
+        <v>0.00053271774718806526</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0040081205292650125</v>
       </c>
       <c r="B76">
-        <v>0.00053670857722109471</v>
+        <v>0.00042555003454281166</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0033401004410541766</v>
       </c>
       <c r="B77">
-        <v>0.00042088869650247035</v>
+        <v>0.00031728126481699221</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0026720803528433416</v>
       </c>
       <c r="B78">
-        <v>0.00030318093526941151</v>
+        <v>0.00020899010283168378</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0020040602646325062</v>
       </c>
       <c r="B79">
-        <v>0.00018516161823994707</v>
+        <v>0.00010259433533708789</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0013360401764216708</v>
       </c>
       <c r="B80">
-        <v>6.9679396847661783E-05</v>
+        <v>1.5413478501566174E-06</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00066802008821083541</v>
       </c>
       <c r="B81">
-        <v>-3.6074017049959169E-05</v>
+        <v>-8.5507503577560964E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00072559700951378226</v>
       </c>
       <c r="B2">
-        <v>0.0006085406224525207</v>
+        <v>0.00071592897986056032</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0014511940190275645</v>
       </c>
       <c r="B3">
-        <v>0.00097038094823146217</v>
+        <v>0.0011184027381722739</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0021767910285413468</v>
       </c>
       <c r="B4">
-        <v>0.0012868490904117058</v>
+        <v>0.0014662166711635126</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.002902388038055129</v>
       </c>
       <c r="B5">
-        <v>0.0015692971333471568</v>
+        <v>0.0017739154900300433</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0036279850475689109</v>
       </c>
       <c r="B6">
-        <v>0.0018224421818185098</v>
+        <v>0.0020475169779843984</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0043535820570826935</v>
       </c>
       <c r="B7">
-        <v>0.0020490291686879845</v>
+        <v>0.0022905078534541708</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0050791790665964754</v>
       </c>
       <c r="B8">
-        <v>0.0022507234726738641</v>
+        <v>0.002504989030634223</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0058047760761102581</v>
       </c>
       <c r="B9">
-        <v>0.0024300363437382692</v>
+        <v>0.0026941536552012859</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.00653037308562404</v>
       </c>
       <c r="B10">
-        <v>0.0025896621041107339</v>
+        <v>0.00286143244466325</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0072559700951378217</v>
       </c>
       <c r="B11">
-        <v>0.0027321814938466135</v>
+        <v>0.0030101141723707725</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0079815671046516053</v>
       </c>
       <c r="B12">
-        <v>0.0028590114294972475</v>
+        <v>0.003141993230794473</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0087071641141653871</v>
       </c>
       <c r="B13">
-        <v>0.0029670271157720882</v>
+        <v>0.0032530284330420404</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0094327611236791689</v>
       </c>
       <c r="B14">
-        <v>0.0030543850985629076</v>
+        <v>0.0033408279230520387</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.010158358133192951</v>
       </c>
       <c r="B15">
-        <v>0.0031289090003326493</v>
+        <v>0.0034154327474494517</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.010883955142706733</v>
       </c>
       <c r="B16">
-        <v>0.0031977742475431249</v>
+        <v>0.0034860521436925048</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.011609552152220516</v>
       </c>
       <c r="B17">
-        <v>0.0032558964060804591</v>
+        <v>0.0035461352098859716</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.012335149161734298</v>
       </c>
       <c r="B18">
-        <v>0.0032966896139911667</v>
+        <v>0.0035872026208291332</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.01306074617124808</v>
       </c>
       <c r="B19">
-        <v>0.0033198221585390153</v>
+        <v>0.0036088214974527512</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.013786343180761862</v>
       </c>
       <c r="B20">
-        <v>0.0033265258642920831</v>
+        <v>0.0036125705722204579</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.014511940190275643</v>
       </c>
       <c r="B21">
-        <v>0.00331803255581845</v>
+        <v>0.003600028577595886</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.015237537199789427</v>
       </c>
       <c r="B22">
-        <v>0.0032953522367220626</v>
+        <v>0.003572490694920283</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.015963134209303211</v>
       </c>
       <c r="B23">
-        <v>0.0032586076267503389</v>
+        <v>0.0035301179010453583</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.016688731218816991</v>
       </c>
       <c r="B24">
-        <v>0.0032076996246865642</v>
+        <v>0.0034727876217004365</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.017414328228330774</v>
       </c>
       <c r="B25">
-        <v>0.003142529129314025</v>
+        <v>0.003400377282614843</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.018139925237844554</v>
       </c>
       <c r="B26">
-        <v>0.0030629558470922995</v>
+        <v>0.0033127129769740214</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.018865522247358338</v>
       </c>
       <c r="B27">
-        <v>0.0029686747151861331</v>
+        <v>0.0032094154677878937</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.019591119256872121</v>
       </c>
       <c r="B28">
-        <v>0.0028593394784365649</v>
+        <v>0.0030900541855225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.0203167162663859</v>
       </c>
       <c r="B29">
-        <v>0.0027346038816846328</v>
+        <v>0.0029541985606438832</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.021042313275899685</v>
       </c>
       <c r="B30">
-        <v>0.0025942766600172457</v>
+        <v>0.0028016190711346593</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.021767910285413465</v>
       </c>
       <c r="B31">
-        <v>0.0024387865095047917</v>
+        <v>0.0026328903850437492</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.022493507294927249</v>
       </c>
       <c r="B32">
-        <v>0.0022687171164635263</v>
+        <v>0.0024487882179366482</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.023219104304441032</v>
       </c>
       <c r="B33">
-        <v>0.002084652167209709</v>
+        <v>0.0022500882853788515</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.023944701313954812</v>
       </c>
       <c r="B34">
-        <v>0.0018869077887575668</v>
+        <v>0.0020372244243599845</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.024670298323468596</v>
       </c>
       <c r="B35">
-        <v>0.0016747298709132144</v>
+        <v>0.0018092629575661833</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.025395895332982376</v>
       </c>
       <c r="B36">
-        <v>0.0014470967441807376</v>
+        <v>0.0015649283291077135</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.02612149234249616</v>
       </c>
       <c r="B37">
-        <v>0.0012029867390642192</v>
+        <v>0.0013029449830948376</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.026847089352009943</v>
       </c>
       <c r="B38">
-        <v>0.00094073217755462932</v>
+        <v>0.0010212090307361872</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.027572686361523723</v>
       </c>
       <c r="B39">
-        <v>0.000656081347590471</v>
+        <v>0.00071430325163385688</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.028298283371037507</v>
       </c>
       <c r="B40">
-        <v>0.00034413652859713171</v>
+        <v>0.00037598209248830691</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.028298283371037507</v>
       </c>
       <c r="B43">
-        <v>0.00012121758135890552</v>
+        <v>8.937201746773029E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.027572686361523723</v>
       </c>
       <c r="B44">
-        <v>0.00024852801928677067</v>
+        <v>0.00019030611524338485</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.026847089352009943</v>
       </c>
       <c r="B45">
-        <v>0.0003773942052837225</v>
+        <v>0.00029691735210216443</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.02612149234249616</v>
       </c>
       <c r="B46">
-        <v>0.00050327903084988865</v>
+        <v>0.00040332078681927015</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.025395895332982376</v>
       </c>
       <c r="B47">
-        <v>0.00062227564969190416</v>
+        <v>0.00050444406476492817</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.024670298323468596</v>
       </c>
       <c r="B48">
-        <v>0.00073299826434243228</v>
+        <v>0.00059846517768946347</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.023944701313954812</v>
       </c>
       <c r="B49">
-        <v>0.00083469133954064488</v>
+        <v>0.00068437470393822755</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.023219104304441032</v>
       </c>
       <c r="B50">
-        <v>0.00092659934002571262</v>
+        <v>0.00076116322185657025</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.022493507294927249</v>
       </c>
       <c r="B51">
-        <v>0.00100821940615168</v>
+        <v>0.00082814830467855909</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.021767910285413465</v>
       </c>
       <c r="B52">
-        <v>0.0010800593807320871</v>
+        <v>0.00088595550519312953</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.021042313275899685</v>
       </c>
       <c r="B53">
-        <v>0.0011428797821953476</v>
+        <v>0.00093553737107793375</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.0203167162663859</v>
       </c>
       <c r="B54">
-        <v>0.0011974411289698756</v>
+        <v>0.00097784645001062478</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.019591119256872121</v>
       </c>
       <c r="B55">
-        <v>0.0012443365288350124</v>
+        <v>0.0010136218217490765</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.018865522247358338</v>
       </c>
       <c r="B56">
-        <v>0.0012834894469738094</v>
+        <v>0.0010427486943720488</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.018139925237844554</v>
       </c>
       <c r="B57">
-        <v>0.0013146559379202463</v>
+        <v>0.0010648988080385244</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.017414328228330774</v>
       </c>
       <c r="B58">
-        <v>0.0013375920562083024</v>
+        <v>0.0010797439029074847</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.016688731218816991</v>
       </c>
       <c r="B59">
-        <v>0.0013520836455894582</v>
+        <v>0.0010869956485755859</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.015963134209303211</v>
       </c>
       <c r="B60">
-        <v>0.0013580357066852004</v>
+        <v>0.0010865254323901808</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.015237537199789427</v>
       </c>
       <c r="B61">
-        <v>0.001355383029334517</v>
+        <v>0.0010782445711362962</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.014511940190275643</v>
       </c>
       <c r="B62">
-        <v>0.0013440604033763954</v>
+        <v>0.0010620643815989594</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.013786343180761862</v>
       </c>
       <c r="B63">
-        <v>0.001324212908793458</v>
+        <v>0.0010381682008650834</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.01306074617124808</v>
       </c>
       <c r="B64">
-        <v>0.0012968267861428627</v>
+        <v>0.001007827447229127</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.012335149161734298</v>
       </c>
       <c r="B65">
-        <v>0.0012630985661254025</v>
+        <v>0.00097258555928743623</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.011609552152220516</v>
       </c>
       <c r="B66">
-        <v>0.0012242247794418688</v>
+        <v>0.00093398597563635612</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.010883955142706733</v>
       </c>
       <c r="B67">
-        <v>0.0011798289744974647</v>
+        <v>0.00089155107834808494</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.010158358133192951</v>
       </c>
       <c r="B68">
-        <v>0.0011232427705150331</v>
+        <v>0.00083671902339823082</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0094327611236791689</v>
       </c>
       <c r="B69">
-        <v>0.0010492853271389917</v>
+        <v>0.00076284250264986109</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0087071641141653871</v>
       </c>
       <c r="B70">
-        <v>0.00096501789488242151</v>
+        <v>0.00067901657761246931</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0079815671046516053</v>
       </c>
       <c r="B71">
-        <v>0.00087813882041667068</v>
+        <v>0.00059515701911944563</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0072559700951378217</v>
       </c>
       <c r="B72">
-        <v>0.00078665274417749989</v>
+        <v>0.00050872006565334089</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.00653037308562404</v>
       </c>
       <c r="B73">
-        <v>0.00068726972024312253</v>
+        <v>0.00041549937969060681</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0058047760761102581</v>
       </c>
       <c r="B74">
-        <v>0.00058121516349715228</v>
+        <v>0.00031709785203413559</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0050791790665964754</v>
       </c>
       <c r="B75">
-        <v>0.00047086456695135119</v>
+        <v>0.00021659900899099235</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0043535820570826935</v>
       </c>
       <c r="B76">
-        <v>0.00035867837532467707</v>
+        <v>0.00011719969055849052</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0036279850475689109</v>
       </c>
       <c r="B77">
-        <v>0.0002469186086572883</v>
+        <v>2.1843812491399631E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.002902388038055129</v>
       </c>
       <c r="B78">
-        <v>0.00013696863656695107</v>
+        <v>-6.7649720115935336E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0021767910285413468</v>
       </c>
       <c r="B79">
-        <v>3.1276025149056696E-05</v>
+        <v>-0.0001480915556027501</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0014511940190275645</v>
       </c>
       <c r="B80">
-        <v>-6.5771581354218621E-05</v>
+        <v>-0.00021379337129503009</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00072559700951378226</v>
       </c>
       <c r="B81">
-        <v>-0.00014317787940375772</v>
+        <v>-0.00025056623681179741</v>
       </c>
     </row>
     <row r="82" spans="1:2">
